--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37A.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750AEB3F-5AC7-4ACF-9AFC-E673AF855DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="228">
   <si>
     <t>49001</t>
   </si>
@@ -114,9 +120,6 @@
     <t>436812</t>
   </si>
   <si>
-    <t>436802</t>
-  </si>
-  <si>
     <t>436805</t>
   </si>
   <si>
@@ -168,53 +171,56 @@
     <t>Fecha de término recepción de las propuestas</t>
   </si>
   <si>
-    <t>Área(s) y servidor(es) público(s) con los que se podrá establecer contacto 
+    <t>Área(s) y persona(s) servidora(s) pública(s) con las que se podrá establecer contacto 
 Tabla_436804</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>6230087</t>
-  </si>
-  <si>
-    <t>0A6834366A7062DDDD6B9A11C012E64A</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>Artículos 29 y 30 del Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>6649126</t>
-  </si>
-  <si>
-    <t>Subdireccion de Actividades Paraescolares</t>
-  </si>
-  <si>
-    <t>13/07/2023</t>
-  </si>
-  <si>
-    <t>Del periodo 01 de abril del 2023 al 30 de junio del 2023, El Colegio de Bachilleres del Estado de Tlaxcala a través de la Subdirección de Actividades Paraescolares no se generarón mecanismos de participación ciudadana, con referencia a los artículos 29 y 30 del Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala, toda vez que dentro de sus facultades del organismo desconcentrado, no efectúa este tipo de actividades, en consecuencia no cuenta con un hipervinculo.</t>
+    <t>Articulo 29 y 30 reglamento Interior del Organismo Público Desconsentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>16340311</t>
+  </si>
+  <si>
+    <t>Subdirección de Actividades Paraescolares</t>
+  </si>
+  <si>
+    <t>15970637</t>
+  </si>
+  <si>
+    <t>1CB8AC16D0BEF1628FA14CED4D661E9A</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>14434217</t>
+  </si>
+  <si>
+    <t>05/07/2024</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de abril al 30 de junio del 2024, El Colegio de Bachilleres del Estado de Tlaxcala a traves de la Subdirección de Actividades Paraescolares no se generarón mecanismos de participación cuidadana con referencia a los articulos 29 y 30 del Reglamento Interior del Organismo Público Desconsentrado Colegio de Bachilleres del Estado de Tlaxcala, toda vez que dentro de sus facultades del organismo desconcentrado no afécta este tipo de actividades en consecuencia no cuenta con un hipervinculo.</t>
+  </si>
+  <si>
+    <t>9958118</t>
   </si>
   <si>
     <t>9</t>
@@ -292,13 +298,13 @@
     <t xml:space="preserve">Nombre del(as) área(s) que gestiona el mecanismo de participación </t>
   </si>
   <si>
-    <t>Nombre(s) del/la Servidor(a) Público(a) de contacto</t>
-  </si>
-  <si>
-    <t>Primer apellido del/la servidor(a) público(a) de contacto</t>
-  </si>
-  <si>
-    <t>Segundo apellido del/la servidor(a) público(a) de contacto</t>
+    <t>Nombre(s) de la persona servidora pública de contacto</t>
+  </si>
+  <si>
+    <t>Primer apellido de la persona servidora pública de contacto</t>
+  </si>
+  <si>
+    <t>Segundo apellido de la persona servidora pública de contacto</t>
   </si>
   <si>
     <t>Sexo (catálogo)</t>
@@ -355,81 +361,87 @@
     <t>Horario y días de atención</t>
   </si>
   <si>
-    <t>BD0B4EC0657B56EA8709C2DC1A9802E1</t>
-  </si>
-  <si>
-    <t>Subdirección de Actividades Paraescolares</t>
-  </si>
-  <si>
-    <t>Alejandro Alonso</t>
-  </si>
-  <si>
-    <t>Herrera</t>
-  </si>
-  <si>
-    <t>Lumbreras</t>
-  </si>
-  <si>
-    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+    <t>99E5FD1B8F2FBAD759E9CFB8B7282DD1</t>
+  </si>
+  <si>
+    <t>Iliana Belem</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>sub.paraescolares@cobatlaxcala.edu.mx</t>
   </si>
   <si>
+    <t>Avenida</t>
+  </si>
+  <si>
     <t>Miguel N. Lira</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Centro</t>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>Tlaxcala</t>
+    <t>Colonia Centro</t>
   </si>
   <si>
     <t>90000</t>
   </si>
   <si>
-    <t>4620026</t>
-  </si>
-  <si>
-    <t>Lunes a Viernes 8:30 a 175:30</t>
-  </si>
-  <si>
-    <t>3150F3C209CC56190A462116B04F4F14</t>
+    <t>2466893134</t>
+  </si>
+  <si>
+    <t>8:00 a 17:30</t>
+  </si>
+  <si>
+    <t>79CFCE74E6EAE44F7725044248DDFC5A</t>
+  </si>
+  <si>
+    <t>Ismerati</t>
+  </si>
+  <si>
+    <t>Contreras</t>
+  </si>
+  <si>
+    <t>Flores</t>
+  </si>
+  <si>
+    <t>80EF8847016340AD2FF7E81A1DE3FA0B</t>
+  </si>
+  <si>
+    <t>Ismerai</t>
+  </si>
+  <si>
+    <t>E5B5CC6D286D2E0F65F456F054BE76B1</t>
+  </si>
+  <si>
+    <t>Subirección de Actividades Paraescolares</t>
+  </si>
+  <si>
+    <t>Carretera</t>
+  </si>
+  <si>
+    <t>2464620026</t>
   </si>
   <si>
     <t>Hombre</t>
   </si>
   <si>
-    <t>Carretera</t>
-  </si>
-  <si>
-    <t>Miguel N Lira</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Tlaxcala, centro</t>
-  </si>
-  <si>
-    <t>Colonia Centro</t>
-  </si>
-  <si>
-    <t>246 46 2 00 26 Ext. 116</t>
-  </si>
-  <si>
-    <t>8:30 a 17:30</t>
-  </si>
-  <si>
-    <t>Mujer</t>
-  </si>
-  <si>
     <t>Privada</t>
   </si>
   <si>
@@ -500,9 +512,6 @@
   </si>
   <si>
     <t>Periférico</t>
-  </si>
-  <si>
-    <t>Avenida</t>
   </si>
   <si>
     <t>Parque industrial</t>
@@ -712,7 +721,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -811,6 +820,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -826,44 +838,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -891,14 +903,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -926,6 +955,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -937,180 +983,156 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="107" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="102.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="46.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="45.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -1120,19 +1142,18 @@
     <col min="13" max="13" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="37.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="72.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="255" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1149,7 +1170,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1164,7 +1185,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1214,16 +1235,13 @@
         <v>8</v>
       </c>
       <c r="R4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S4" t="s">
-        <v>11</v>
-      </c>
-      <c r="T4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1278,13 +1296,10 @@
       <c r="S5" t="s">
         <v>30</v>
       </c>
-      <c r="T5" t="s">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1304,132 +1319,125 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-    </row>
-    <row r="7" spans="1:20" ht="39" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:19" ht="39" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>59</v>
       </c>
       <c r="Q8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>62</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:T6"/>
+    <mergeCell ref="A6:S6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1442,17 +1450,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="72.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="65.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -1682,31 +1690,31 @@
     </row>
     <row r="4" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>116</v>
@@ -1715,131 +1723,279 @@
         <v>117</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="U4" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="H5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>117</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="P5" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="Q7" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="U5" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>132</v>
+      <c r="T7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>Hidden_1_Tabla_4368046</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>Hidden_2_Tabla_4368048</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M4:M201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M4:M201" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>Hidden_3_Tabla_43680412</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T4:T201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T4:T201" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>Hidden_4_Tabla_43680419</formula1>
     </dataValidation>
   </dataValidations>
@@ -1848,18 +2004,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1868,138 +2024,138 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2008,213 +2164,213 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2223,168 +2379,168 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750AEB3F-5AC7-4ACF-9AFC-E673AF855DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64B8FBE-DE7F-403F-B4E7-037310B284D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -199,25 +199,25 @@
     <t>Subdirección de Actividades Paraescolares</t>
   </si>
   <si>
+    <t>46E5F5E424803A9509AC8D5C0ED6460B</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>15970637</t>
   </si>
   <si>
-    <t>1CB8AC16D0BEF1628FA14CED4D661E9A</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
+    <t>03/10/2024</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de julio al 30 de septiembre del 2024, El Colegio de Bachilleres del Estado de Tlaxcala a traves de la Subdirección de Actividades Paraescolares no se generarón mecanismos de participación cuidadana con referencia a los articulos 29 y 30 del Reglamento Interior del Organismo Público Desconsentrado Colegio de Bachilleres del Estado de Tlaxcala, toda vez que dentro de sus facultades del organismo desconcentrado no afécta este tipo de actividades en consecuencia no cuenta con un hipervinculo.</t>
   </si>
   <si>
     <t>14434217</t>
-  </si>
-  <si>
-    <t>05/07/2024</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril al 30 de junio del 2024, El Colegio de Bachilleres del Estado de Tlaxcala a traves de la Subdirección de Actividades Paraescolares no se generarón mecanismos de participación cuidadana con referencia a los articulos 29 y 30 del Reglamento Interior del Organismo Público Desconsentrado Colegio de Bachilleres del Estado de Tlaxcala, toda vez que dentro de sus facultades del organismo desconcentrado no afécta este tipo de actividades en consecuencia no cuenta con un hipervinculo.</t>
   </si>
   <si>
     <t>9958118</t>
@@ -1378,16 +1378,16 @@
     </row>
     <row r="8" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>51</v>
@@ -1423,16 +1423,16 @@
         <v>51</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="5" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>125</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="6" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>129</v>
